--- a/store/May-2026/Mail Attachment/Non_BTC_Report_May-2026.xlsx
+++ b/store/May-2026/Mail Attachment/Non_BTC_Report_May-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,263 +512,6 @@
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PackageName</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WTI-20260531-3905961</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nishant Marathe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BP Business Solutions India Private Ltd- SEZ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DUSHYANT SHARMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-31 12:00:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>7619401840</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>dushyant.sharma@uk.bp.com</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PG link</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Naveen S</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-05-31 10:40:40.653000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WTI-20260531-3905943</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IBM India Private Limited</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SRIJANI BHATTACHARYA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-31 17:40:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>8334003222</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>sarmistha.sarma@in.ibm.com</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PG link</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yudhveer Singh W04209</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-05-31 09:56:31.423000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Apt.Transfer / Office Drop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Airport - Transfer Rate : 1500.00 ] PkgID:[212268]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WTI-20260531-3905966</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IBM India Private Limited</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ARUNAVA SAHA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-31 23:45:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9903977113</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Arunava.saha@in.ibm.com</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PG link</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yudhveer Singh W04209</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-05-31 10:45:26.210000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Kolkata Hub</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Apt.Transfer / Office Drop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Airport - Transfer Rate : 1500.00 ] PkgID:[212593]</t>
         </is>
       </c>
     </row>
